--- a/resources/city/building.xlsx
+++ b/resources/city/building.xlsx
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -466,9 +466,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1053,7 +1050,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.29071428571428" bestFit="1" customWidth="1" style="63" min="1" max="1"/>
@@ -1194,91 +1191,91 @@
       <c r="K3" s="47" t="n"/>
     </row>
     <row r="4" ht="19.5" customFormat="1" customHeight="1" s="19">
-      <c r="A4" s="69" t="n">
-        <v>12</v>
+      <c r="A4" s="55" t="n">
+        <v>101</v>
       </c>
       <c r="B4" s="56" t="n"/>
       <c r="C4" s="56" t="inlineStr">
         <is>
-          <t>聚灵塔</t>
+          <t>帮派基地</t>
         </is>
       </c>
       <c r="D4" s="57" t="n">
-        <v>4012</v>
+        <v>4005</v>
       </c>
       <c r="E4" s="56" t="inlineStr">
         <is>
-          <t>ResidenceBuildingCollect</t>
+          <t>CityGuildBaseBuilding</t>
         </is>
       </c>
       <c r="F4" s="58" t="n"/>
       <c r="G4" s="55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H4" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="55" t="n"/>
-      <c r="J4" s="56" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I4" s="55" t="n">
+        <v>1043</v>
+      </c>
+      <c r="J4" s="56" t="n"/>
       <c r="K4" s="58" t="n"/>
     </row>
     <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="55" t="n">
-        <v>101</v>
-      </c>
-      <c r="B5" s="56" t="n"/>
-      <c r="C5" s="56" t="inlineStr">
-        <is>
-          <t>帮派基地</t>
-        </is>
-      </c>
-      <c r="D5" s="57" t="n">
-        <v>4005</v>
-      </c>
-      <c r="E5" s="56" t="inlineStr">
-        <is>
-          <t>CityGuildBaseBuilding</t>
-        </is>
-      </c>
-      <c r="F5" s="58" t="n"/>
-      <c r="G5" s="55" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" s="55" t="n">
+      <c r="A5" s="59" t="n">
+        <v>102</v>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>坊市</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>4015</v>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>CityMarketBuilding</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="I5" s="55" t="n">
+      <c r="H5" s="59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="59" t="n">
         <v>1043</v>
       </c>
-      <c r="J5" s="56" t="n"/>
+      <c r="J5" s="15" t="n"/>
       <c r="K5" s="58" t="n"/>
     </row>
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="59" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B6" s="15" t="n"/>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>坊市</t>
-        </is>
-      </c>
-      <c r="D6" s="32" t="n">
-        <v>4015</v>
+          <t>传送阵</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="n">
+        <v>4009</v>
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>CityMarketBuilding</t>
+          <t>CityTeleporterBuilding</t>
         </is>
       </c>
       <c r="F6" s="33" t="n"/>
       <c r="G6" s="59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="59" t="n">
         <v>1043</v>
@@ -1288,28 +1285,28 @@
     </row>
     <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="59" t="n">
-        <v>103</v>
+        <v>201</v>
       </c>
       <c r="B7" s="15" t="n"/>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>传送阵</t>
-        </is>
-      </c>
-      <c r="D7" s="60" t="n">
-        <v>4009</v>
+          <t>城主府</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>4016</v>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>CityTeleporterBuilding</t>
+          <t>CityHallBuilding</t>
         </is>
       </c>
       <c r="F7" s="33" t="n"/>
       <c r="G7" s="59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" s="59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7" s="59" t="n">
         <v>1043</v>
@@ -1319,28 +1316,30 @@
     </row>
     <row r="8" ht="19.5" customHeight="1">
       <c r="A8" s="59" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B8" s="15" t="n"/>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>城主府</t>
+          <t>青龙图腾</t>
         </is>
       </c>
       <c r="D8" s="32" t="n">
-        <v>4016</v>
+        <v>4012</v>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>CityHallBuilding</t>
-        </is>
-      </c>
-      <c r="F8" s="33" t="n"/>
+          <t>CityTotemBuilding</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="n">
+        <v>10047</v>
+      </c>
       <c r="G8" s="59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" s="59" t="n">
         <v>1043</v>
@@ -1350,12 +1349,12 @@
     </row>
     <row r="9" ht="19.5" customHeight="1">
       <c r="A9" s="59" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B9" s="15" t="n"/>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>青龙图腾</t>
+          <t>白虎图腾</t>
         </is>
       </c>
       <c r="D9" s="32" t="n">
@@ -1367,7 +1366,7 @@
         </is>
       </c>
       <c r="F9" s="33" t="n">
-        <v>10047</v>
+        <v>10048</v>
       </c>
       <c r="G9" s="59" t="n">
         <v>1</v>
@@ -1383,12 +1382,12 @@
     </row>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="59" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B10" s="15" t="n"/>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>白虎图腾</t>
+          <t>朱雀图腾</t>
         </is>
       </c>
       <c r="D10" s="32" t="n">
@@ -1400,7 +1399,7 @@
         </is>
       </c>
       <c r="F10" s="33" t="n">
-        <v>10048</v>
+        <v>10049</v>
       </c>
       <c r="G10" s="59" t="n">
         <v>1</v>
@@ -1416,12 +1415,12 @@
     </row>
     <row r="11" ht="19.5" customHeight="1">
       <c r="A11" s="59" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" s="15" t="n"/>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>朱雀图腾</t>
+          <t>玄武图腾</t>
         </is>
       </c>
       <c r="D11" s="32" t="n">
@@ -1433,7 +1432,7 @@
         </is>
       </c>
       <c r="F11" s="33" t="n">
-        <v>10049</v>
+        <v>10050</v>
       </c>
       <c r="G11" s="59" t="n">
         <v>1</v>
@@ -1449,30 +1448,30 @@
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="59" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B12" s="15" t="n"/>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>玄武图腾</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="n">
-        <v>4012</v>
+          <t>东木门</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="n">
+        <v>4009</v>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>CityTotemBuilding</t>
-        </is>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>10050</v>
-      </c>
-      <c r="G12" s="59" t="n">
-        <v>1</v>
+          <t>CityGateBuilding</t>
+        </is>
+      </c>
+      <c r="F12" s="61" t="n">
+        <v>10056</v>
+      </c>
+      <c r="G12" s="62" t="n">
+        <v>5</v>
       </c>
       <c r="H12" s="59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="59" t="n">
         <v>1043</v>
@@ -1482,12 +1481,12 @@
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="59" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B13" s="15" t="n"/>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>东木门</t>
+          <t>南火门</t>
         </is>
       </c>
       <c r="D13" s="60" t="n">
@@ -1515,12 +1514,12 @@
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="59" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B14" s="15" t="n"/>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>南火门</t>
+          <t>西金门</t>
         </is>
       </c>
       <c r="D14" s="60" t="n">
@@ -1548,12 +1547,12 @@
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="59" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B15" s="15" t="n"/>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>西金门</t>
+          <t>北水门</t>
         </is>
       </c>
       <c r="D15" s="60" t="n">
@@ -1581,12 +1580,12 @@
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="59" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>北水门</t>
+          <t>守方大营门</t>
         </is>
       </c>
       <c r="D16" s="60" t="n">
@@ -1598,13 +1597,13 @@
         </is>
       </c>
       <c r="F16" s="61" t="n">
-        <v>10056</v>
+        <v>10058</v>
       </c>
       <c r="G16" s="62" t="n">
         <v>5</v>
       </c>
       <c r="H16" s="59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16" s="59" t="n">
         <v>1043</v>
@@ -1614,30 +1613,30 @@
     </row>
     <row r="17" ht="19.5" customHeight="1">
       <c r="A17" s="59" t="n">
-        <v>210</v>
+        <v>301</v>
       </c>
       <c r="B17" s="15" t="n"/>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>守方大营门</t>
-        </is>
-      </c>
-      <c r="D17" s="60" t="n">
-        <v>4009</v>
+          <t>仙圃</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>4010</t>
+        </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>CityGateBuilding</t>
-        </is>
-      </c>
-      <c r="F17" s="61" t="n">
-        <v>10058</v>
-      </c>
-      <c r="G17" s="62" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="59" t="n">
-        <v>4</v>
+          <t>CityFairyGardenBuilding</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="n"/>
+      <c r="G17" s="60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="60" t="n">
+        <v>2</v>
       </c>
       <c r="I17" s="59" t="n">
         <v>1043</v>
@@ -1647,29 +1646,27 @@
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="59" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B18" s="15" t="n"/>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>仙圃</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
-        <is>
-          <t>4010</t>
-        </is>
+          <t>镇妖阵</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>4013</v>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>CityFairyGardenBuilding</t>
+          <t>CityDemonArrayBuilding</t>
         </is>
       </c>
       <c r="F18" s="33" t="n"/>
-      <c r="G18" s="60" t="n">
+      <c r="G18" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="60" t="n">
+      <c r="H18" s="59" t="n">
         <v>2</v>
       </c>
       <c r="I18" s="59" t="n">
@@ -1680,28 +1677,28 @@
     </row>
     <row r="19" ht="19.5" customHeight="1">
       <c r="A19" s="59" t="n">
-        <v>302</v>
+        <v>401</v>
       </c>
       <c r="B19" s="15" t="n"/>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>镇妖阵</t>
+          <t>锻造台</t>
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>4013</v>
+        <v>4010</v>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>CityDemonArrayBuilding</t>
+          <t>CityCraftBuilding</t>
         </is>
       </c>
       <c r="F19" s="33" t="n"/>
-      <c r="G19" s="59" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="59" t="n">
-        <v>2</v>
+      <c r="G19" s="60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="60" t="n">
+        <v>3</v>
       </c>
       <c r="I19" s="59" t="n">
         <v>1043</v>
@@ -1711,12 +1708,12 @@
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="A20" s="59" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B20" s="15" t="n"/>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>锻造台</t>
+          <t>裁缝台</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
@@ -1742,12 +1739,12 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="59" t="n">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B21" s="15" t="n"/>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>裁缝台</t>
+          <t>炼金台</t>
         </is>
       </c>
       <c r="D21" s="32" t="n">
@@ -1772,153 +1769,32 @@
       <c r="K21" s="58" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="59" t="n">
-        <v>403</v>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>炼金台</t>
-        </is>
-      </c>
-      <c r="D22" s="32" t="n">
-        <v>4010</v>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>瞭望塔</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4333</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>CityCraftBuilding</t>
         </is>
       </c>
-      <c r="F22" s="33" t="n"/>
-      <c r="G22" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="59" t="n">
-        <v>1043</v>
-      </c>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="58" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="69" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>瞭望塔</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4333</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CityCraftBuilding</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="69" t="n">
-        <v>506</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>种田产出</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>初级灵田</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="69" t="n">
-        <v>507</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>洞府类别，归属种田产出用途，允许摆放单一实例的初级灵田，需图纸道具10072，准入等级为入门级</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>初级灵田</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="69" t="n">
-        <v>508</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>洞府类别，归属种田产出用途，允许摆放单一实例的初级灵田，需图纸道具10072，准入等级为入门级</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>初级灵田</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="69" t="inlineStr">
-        <is>
-          <t>洞府</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>种田产出用途</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>初级灵田</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="69" t="n"/>
-      <c r="C28" t="inlineStr">
-        <is>
           <t>两仪台</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F23" t="n">
         <v>6666</v>
       </c>
     </row>
